--- a/00_output/11_avoided_costs.xlsx
+++ b/00_output/11_avoided_costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>summer_gener._capacity_usdperKWH</t>
+          <t>summer_gener_capacity_usdperKWH</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -531,6 +531,56 @@
     <row r="11">
       <c r="A11" t="n">
         <v>2035</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2045</v>
       </c>
     </row>
   </sheetData>

--- a/00_output/11_avoided_costs.xlsx
+++ b/00_output/11_avoided_costs.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -42,12 +57,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,175 +458,431 @@
   </sheetPr>
   <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="33" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="29" customWidth="1" min="12" max="12"/>
+    <col width="37" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>summer_on-peak_usdperKWH</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>summer_off-peak_usdperKWH</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>winter_on-peak_usdperKWH</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>winter_off-peak_usdperKWH</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>shoulder_on-peak_usdperKWH</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>shoulder_off-peak_usdperKWH</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>summer_gener_capacity_usdperKWH</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>winter_gener_capacity_usdperKWH</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>summer_td_usdperKWH</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>winter_td_usdperKWH</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>oil_residential_usdperMMBtu</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>natural_gas_residential_usdperMMBtu</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="2" t="n">
         <v>2026</v>
       </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="4" t="n">
         <v>2027</v>
       </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="2" t="n">
         <v>2028</v>
       </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="4" t="n">
         <v>2029</v>
       </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="2" t="n">
         <v>2030</v>
       </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="4" t="n">
         <v>2031</v>
       </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="2" t="n">
         <v>2032</v>
       </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="4" t="n">
         <v>2033</v>
       </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="2" t="n">
         <v>2034</v>
       </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="4" t="n">
         <v>2035</v>
       </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="2" t="n">
         <v>2036</v>
       </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="4" t="n">
         <v>2037</v>
       </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="2" t="n">
         <v>2038</v>
       </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="4" t="n">
         <v>2039</v>
       </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="2" t="n">
         <v>2040</v>
       </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="4" t="n">
         <v>2041</v>
       </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="2" t="n">
         <v>2042</v>
       </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="4" t="n">
         <v>2043</v>
       </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="2" t="n">
         <v>2044</v>
       </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="4" t="n">
         <v>2045</v>
       </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/00_output/11_avoided_costs.xlsx
+++ b/00_output/11_avoided_costs.xlsx
@@ -459,7 +459,7 @@
   <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
